--- a/test_cases/regcv2_testbench.xlsx
+++ b/test_cases/regcv2_testbench.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="74">
   <si>
     <t>name</t>
   </si>
@@ -51,7 +51,7 @@
     <t>TimeSeries_1</t>
   </si>
   <si>
-    <t>disturbance_profile_15.xlsx</t>
+    <t>disturbance_profile.xlsx</t>
   </si>
   <si>
     <t>PLBVF</t>
@@ -740,7 +740,9 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -1247,7 +1249,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
@@ -1365,6 +1367,7 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="6" spans="8:8" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/test_cases/regcv2_testbench.xlsx
+++ b/test_cases/regcv2_testbench.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="74">
   <si>
     <t>name</t>
   </si>
@@ -247,7 +247,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -270,6 +270,11 @@
       <color rgb="FF2C3E50"/>
       <sz val="12"/>
       <name val="Times"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <name val="-apple-system"/>
     </font>
     <font>
       <color rgb="FF2C3E50"/>
@@ -312,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -324,12 +329,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -740,9 +748,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -821,10 +827,10 @@
       <c r="G2">
         <v>0.9</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="4">
         <v>1</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="4">
         <v>0</v>
       </c>
     </row>
@@ -850,7 +856,7 @@
       <c r="G3">
         <v>0.9</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="4">
         <v>1</v>
       </c>
       <c r="I3">
@@ -989,25 +995,25 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J2">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>0.5</v>
+        <v>999</v>
       </c>
       <c r="L2">
-        <v>0.1</v>
+        <v>-999</v>
       </c>
       <c r="M2">
-        <v>0.15</v>
+        <v>999</v>
       </c>
       <c r="N2">
-        <v>-0.4</v>
+        <v>999</v>
       </c>
       <c r="O2">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="P2">
         <v>1.4</v>
@@ -1019,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -1151,13 +1157,13 @@
         <v>34.5</v>
       </c>
       <c r="K2">
-        <v>0.01938</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="M2">
-        <v>0.0528</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -1249,7 +1255,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
@@ -1340,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="K2">
         <v>60</v>
@@ -1367,7 +1373,6 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="8:8" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1496,53 +1501,57 @@
       <c r="F1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
+      <c r="I1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
         <v>0</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="5">
         <v>1</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="5">
         <v>1</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="5">
         <v>1</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="5">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5">
         <v>5</v>
       </c>
-      <c r="H2" s="4">
-        <v>0.11</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="I2" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
       <c r="P2" s="3"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -1653,12 +1662,24 @@
       <c r="G1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -1675,323 +1696,335 @@
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="6">
         <v>1</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="6">
         <v>100</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="6">
         <v>34.5</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <v>2</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
+      <c r="H2" s="7">
+        <v>1</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0</v>
+      </c>
+      <c r="J2" s="6">
+        <v>0</v>
+      </c>
+      <c r="K2" s="6">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6">
+        <v>0</v>
+      </c>
+      <c r="M2" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
